--- a/lease_analyzer/input_data/lease_graphy_information_fy25.xlsx
+++ b/lease_analyzer/input_data/lease_graphy_information_fy25.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\lbh00\OneDrive\문서\감사\감사자료\audit-automation\graphy\감사조서\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\lbh00\OneDrive\문서\감사\감사자료\audit-automation\lease_analyzer\input_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B0BBB5D-8476-4716-AAF3-F5D9194C8038}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E560F6D-0BBF-40C3-8BBD-E609B9531C3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-19298" yWindow="-98" windowWidth="19396" windowHeight="12196" xr2:uid="{454C2771-5E2B-4564-95BC-9D29467E181C}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="16220" xr2:uid="{454C2771-5E2B-4564-95BC-9D29467E181C}"/>
   </bookViews>
   <sheets>
     <sheet name="리스정보" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="34">
   <si>
     <t>계약일반</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -161,6 +161,10 @@
   </si>
   <si>
     <t>기말</t>
+  </si>
+  <si>
+    <t>지급보증금(명목가액)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -256,41 +260,44 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="4" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="4" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -629,358 +636,380 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0902D34D-9C28-4A59-B8DC-510E834E6DF9}">
-  <dimension ref="A1:Q8"/>
+  <dimension ref="A1:R8"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="12.33203125" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.5" style="3" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="24.25" style="3" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="21.5" style="3" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="10.75" style="3" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="19" style="3" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="22.1640625" style="3" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="17.75" style="3" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="23.9140625" style="3" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="18.33203125" style="3" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="10.4140625" style="3" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="26.9140625" style="3" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13.75" style="3" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="19" style="3" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="16.25" style="3" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="21.5" style="3" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="8.6640625" style="3"/>
+    <col min="1" max="1" width="12.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24.25" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="21.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="10.75" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="19" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="22.1640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="17.75" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="23.9140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="18.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.4140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="26.9140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.75" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="19" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="16.25" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="16.25" style="1" customWidth="1"/>
+    <col min="18" max="18" width="21.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="8.6640625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.45">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1" t="s">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.45">
+      <c r="A1" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
+      <c r="E1" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
-      <c r="I1" s="2" t="s">
+      <c r="F1" s="11"/>
+      <c r="G1" s="11"/>
+      <c r="H1" s="11"/>
+      <c r="I1" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="J1" s="2"/>
-      <c r="K1" s="2"/>
-      <c r="L1" s="2"/>
-      <c r="M1" s="2"/>
-      <c r="N1" s="2" t="s">
+      <c r="J1" s="12"/>
+      <c r="K1" s="12"/>
+      <c r="L1" s="12"/>
+      <c r="M1" s="12"/>
+      <c r="N1" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="O1" s="2"/>
-      <c r="P1" s="2"/>
-      <c r="Q1" s="2"/>
+      <c r="O1" s="12"/>
+      <c r="P1" s="12"/>
+      <c r="Q1" s="12"/>
+      <c r="R1" s="12"/>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.45">
-      <c r="A2" s="4" t="s">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.45">
+      <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="E2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="F2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="G2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="H2" s="4" t="s">
+      <c r="H2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="I2" s="4" t="s">
+      <c r="I2" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="J2" s="4" t="s">
+      <c r="J2" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="K2" s="4" t="s">
+      <c r="K2" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="L2" s="4" t="s">
+      <c r="L2" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="M2" s="4" t="s">
+      <c r="M2" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="N2" s="4" t="s">
+      <c r="N2" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="O2" s="4" t="s">
+      <c r="O2" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="P2" s="4" t="s">
+      <c r="P2" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="Q2" s="4" t="s">
+      <c r="Q2" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="R2" s="2" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.45">
-      <c r="A3" s="3">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.45">
+      <c r="A3" s="1">
         <v>1</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="E3" s="5">
+      <c r="E3" s="3">
         <v>45078</v>
       </c>
-      <c r="F3" s="5">
+      <c r="F3" s="3">
         <v>45808</v>
       </c>
-      <c r="G3" s="6" t="s">
+      <c r="G3" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="H3" s="7">
+      <c r="H3" s="5">
         <f>DATEDIF(E3,F3,"M")+1</f>
         <v>24</v>
       </c>
-      <c r="I3" s="8">
+      <c r="I3" s="6">
         <v>1219600</v>
       </c>
-      <c r="J3" s="6" t="s">
+      <c r="J3" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="K3" s="11" t="s">
+      <c r="K3" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="L3" s="9">
+      <c r="L3" s="7">
         <v>9.7599999999999992E-2</v>
       </c>
-      <c r="M3" s="8">
+      <c r="M3" s="6">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="N3" s="6">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="O3" s="6">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="P3" s="6">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="Q3" s="6">
         <v>12196000</v>
       </c>
-      <c r="N3" s="8">
-        <f>0</f>
-        <v>0</v>
-      </c>
-      <c r="O3" s="8">
-        <f>0</f>
-        <v>0</v>
-      </c>
-      <c r="P3" s="8">
-        <f>0</f>
-        <v>0</v>
-      </c>
-      <c r="Q3" s="8">
+      <c r="R3" s="6">
         <f>0</f>
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.45">
-      <c r="A4" s="3">
+    <row r="4" spans="1:18" x14ac:dyDescent="0.45">
+      <c r="A4" s="1">
         <v>2</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="D4" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="E4" s="5">
+      <c r="E4" s="3">
         <v>42968</v>
       </c>
-      <c r="F4" s="5">
+      <c r="F4" s="3">
         <v>45733</v>
       </c>
-      <c r="G4" s="6" t="s">
+      <c r="G4" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="H4" s="10">
+      <c r="H4" s="8">
         <f t="shared" ref="H4:H6" si="0">DATEDIF(E4,F4,"M")</f>
         <v>90</v>
       </c>
-      <c r="I4" s="8">
+      <c r="I4" s="6">
         <v>100000</v>
       </c>
-      <c r="J4" s="6" t="s">
+      <c r="J4" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="K4" s="11" t="s">
+      <c r="K4" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="L4" s="9">
+      <c r="L4" s="7">
         <v>6.4642400000000003E-2</v>
       </c>
-      <c r="M4" s="8">
+      <c r="M4" s="6">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="N4" s="6">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="O4" s="6">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="P4" s="6">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="Q4" s="6">
         <v>110000</v>
       </c>
-      <c r="N4" s="8">
-        <f>0</f>
-        <v>0</v>
-      </c>
-      <c r="O4" s="8">
-        <f>0</f>
-        <v>0</v>
-      </c>
-      <c r="P4" s="8">
-        <f>0</f>
-        <v>0</v>
-      </c>
-      <c r="Q4" s="8">
+      <c r="R4" s="6">
         <f>0</f>
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.45">
-      <c r="A5" s="3">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.45">
+      <c r="A5" s="1">
         <v>3</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="D5" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="E5" s="5">
+      <c r="E5" s="3">
         <v>44137</v>
       </c>
-      <c r="F5" s="5">
+      <c r="F5" s="3">
         <v>45962</v>
       </c>
-      <c r="G5" s="6" t="s">
+      <c r="G5" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="H5" s="7">
+      <c r="H5" s="5">
         <f>DATEDIF(E5,F5,"M")+1</f>
         <v>60</v>
       </c>
-      <c r="I5" s="8">
+      <c r="I5" s="6">
         <v>1399090</v>
       </c>
-      <c r="J5" s="6" t="s">
+      <c r="J5" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="K5" s="11" t="s">
+      <c r="K5" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="L5" s="9">
+      <c r="L5" s="7">
         <v>5.4989999999999997E-2</v>
       </c>
-      <c r="M5" s="8">
+      <c r="M5" s="6">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="N5" s="6">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="O5" s="6">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="P5" s="6">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="Q5" s="6">
         <v>17416000</v>
       </c>
-      <c r="N5" s="8">
-        <f>0</f>
-        <v>0</v>
-      </c>
-      <c r="O5" s="8">
-        <f>0</f>
-        <v>0</v>
-      </c>
-      <c r="P5" s="8">
-        <f>0</f>
-        <v>0</v>
-      </c>
-      <c r="Q5" s="8">
+      <c r="R5" s="6">
         <f>0</f>
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.45">
-      <c r="A6" s="3">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.45">
+      <c r="A6" s="1">
         <v>4</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C6" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="D6" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="E6" s="5">
+      <c r="E6" s="3">
         <v>45112</v>
       </c>
-      <c r="F6" s="5">
+      <c r="F6" s="3">
         <v>46596</v>
       </c>
-      <c r="G6" s="6" t="s">
+      <c r="G6" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="H6" s="10">
+      <c r="H6" s="8">
         <f t="shared" si="0"/>
         <v>48</v>
       </c>
-      <c r="I6" s="8">
+      <c r="I6" s="6">
         <v>710500</v>
       </c>
-      <c r="J6" s="6" t="s">
+      <c r="J6" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="K6" s="11" t="s">
+      <c r="K6" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="L6" s="9">
+      <c r="L6" s="7">
         <v>0.1094</v>
       </c>
-      <c r="M6" s="8">
+      <c r="M6" s="6">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="N6" s="6">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="O6" s="6">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="P6" s="6">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="Q6" s="6">
         <v>8670000</v>
       </c>
-      <c r="N6" s="8">
-        <f>0</f>
-        <v>0</v>
-      </c>
-      <c r="O6" s="8">
-        <f>0</f>
-        <v>0</v>
-      </c>
-      <c r="P6" s="8">
-        <f>0</f>
-        <v>0</v>
-      </c>
-      <c r="Q6" s="8">
+      <c r="R6" s="6">
         <f>0</f>
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.45">
-      <c r="I7" s="8"/>
-      <c r="K7" s="5"/>
-      <c r="L7" s="9"/>
-      <c r="N7" s="8"/>
-      <c r="O7" s="8"/>
-      <c r="P7" s="8"/>
-      <c r="Q7" s="8"/>
+    <row r="7" spans="1:18" x14ac:dyDescent="0.45">
+      <c r="I7" s="6"/>
+      <c r="K7" s="3"/>
+      <c r="L7" s="7"/>
+      <c r="N7" s="6"/>
+      <c r="O7" s="6"/>
+      <c r="P7" s="6"/>
+      <c r="Q7" s="6"/>
+      <c r="R7" s="6"/>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.45">
-      <c r="I8" s="8"/>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.45">
+      <c r="I8" s="6"/>
     </row>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="E1:H1"/>
     <mergeCell ref="I1:M1"/>
-    <mergeCell ref="N1:Q1"/>
+    <mergeCell ref="N1:R1"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="3">
@@ -995,5 +1024,6 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
--- a/lease_analyzer/input_data/lease_graphy_information_fy25.xlsx
+++ b/lease_analyzer/input_data/lease_graphy_information_fy25.xlsx
@@ -586,7 +586,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S8"/>
+  <dimension ref="A1:T8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
     <col width="12.33203125" bestFit="1" customWidth="1" style="1" min="1" max="1"/>
@@ -596,7 +596,7 @@
     <col width="10.75" bestFit="1" customWidth="1" style="1" min="5" max="6"/>
     <col width="19" bestFit="1" customWidth="1" style="1" min="7" max="7"/>
     <col width="22.1640625" bestFit="1" customWidth="1" style="1" min="8" max="8"/>
-    <col width="17.75" bestFit="1" customWidth="1" style="1" min="9" max="9"/>
+    <col width="18.33203125" bestFit="1" customWidth="1" style="1" min="9" max="9"/>
     <col width="23.9140625" bestFit="1" customWidth="1" style="1" min="10" max="10"/>
     <col width="18.33203125" bestFit="1" customWidth="1" style="1" min="11" max="11"/>
     <col width="10.4140625" bestFit="1" customWidth="1" style="1" min="12" max="12"/>
@@ -626,17 +626,8 @@
       <c r="F1" s="13" t="n"/>
       <c r="G1" s="13" t="n"/>
       <c r="H1" s="13" t="n"/>
-      <c r="I1" s="12" t="inlineStr">
-        <is>
-          <t>현금흐름 및 할인율</t>
-        </is>
-      </c>
-      <c r="N1" s="12" t="inlineStr">
-        <is>
-          <t>최초 인식 조정</t>
-        </is>
-      </c>
-      <c r="S1" s="14" t="inlineStr">
+      <c r="I1" s="13" t="n"/>
+      <c r="T1" s="14" t="inlineStr">
         <is>
           <t>원가구분</t>
         </is>
@@ -685,55 +676,60 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
+          <t>상각개시(당월/익월)</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
           <t>정기리스료</t>
         </is>
       </c>
-      <c r="J2" s="2" t="inlineStr">
+      <c r="K2" s="2" t="inlineStr">
         <is>
           <t>지급주기(월/분기/반기/년)</t>
         </is>
       </c>
-      <c r="K2" s="2" t="inlineStr">
+      <c r="L2" s="2" t="inlineStr">
         <is>
           <t>지급시점(기초/기말)</t>
         </is>
       </c>
-      <c r="L2" s="2" t="inlineStr">
+      <c r="M2" s="2" t="inlineStr">
         <is>
           <t>적용할인율</t>
         </is>
       </c>
-      <c r="M2" s="2" t="inlineStr">
+      <c r="N2" s="2" t="inlineStr">
         <is>
           <t>보증잔존가치/매수선택권금액</t>
         </is>
       </c>
-      <c r="N2" s="2" t="inlineStr">
+      <c r="O2" s="2" t="inlineStr">
         <is>
           <t>선급리스료</t>
         </is>
       </c>
-      <c r="O2" s="2" t="inlineStr">
+      <c r="P2" s="2" t="inlineStr">
         <is>
           <t>수취한 리스인센티브</t>
         </is>
       </c>
-      <c r="P2" s="2" t="inlineStr">
+      <c r="Q2" s="2" t="inlineStr">
         <is>
           <t>리스개설직접원가</t>
         </is>
       </c>
-      <c r="Q2" s="10" t="inlineStr">
+      <c r="R2" s="10" t="inlineStr">
         <is>
           <t>지급보증금(명목가액)</t>
         </is>
       </c>
-      <c r="R2" s="2" t="inlineStr">
+      <c r="S2" s="2" t="inlineStr">
         <is>
           <t>복구충당부채(현재가치)</t>
         </is>
       </c>
-      <c r="S2" s="14" t="inlineStr">
+      <c r="T2" s="14" t="inlineStr">
         <is>
           <t>원가구분</t>
         </is>
@@ -773,26 +769,27 @@
         <f>DATEDIF(E3,F3,"M")+1</f>
         <v/>
       </c>
-      <c r="I3" s="16" t="n">
+      <c r="I3" s="9" t="inlineStr">
+        <is>
+          <t>당월</t>
+        </is>
+      </c>
+      <c r="J3" s="16" t="n">
         <v>1219600</v>
       </c>
-      <c r="J3" s="4" t="inlineStr">
+      <c r="K3" s="4" t="inlineStr">
         <is>
           <t>월</t>
         </is>
       </c>
-      <c r="K3" s="9" t="inlineStr">
+      <c r="L3" s="9" t="inlineStr">
         <is>
           <t>기말</t>
         </is>
       </c>
-      <c r="L3" s="7" t="n">
+      <c r="M3" s="7" t="n">
         <v>0.09759999999999999</v>
       </c>
-      <c r="M3" s="16">
-        <f>0</f>
-        <v/>
-      </c>
       <c r="N3" s="16">
         <f>0</f>
         <v/>
@@ -805,14 +802,18 @@
         <f>0</f>
         <v/>
       </c>
-      <c r="Q3" s="16" t="n">
+      <c r="Q3" s="16">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="R3" s="16" t="n">
         <v>12196000</v>
       </c>
-      <c r="R3" s="16">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="S3" t="inlineStr">
+      <c r="S3" s="16">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="T3" s="0" t="inlineStr">
         <is>
           <t>판관비</t>
         </is>
@@ -852,26 +853,27 @@
         <f>DATEDIF(E4,F4,"M")</f>
         <v/>
       </c>
-      <c r="I4" s="16" t="n">
+      <c r="I4" s="9" t="inlineStr">
+        <is>
+          <t>당월</t>
+        </is>
+      </c>
+      <c r="J4" s="16" t="n">
         <v>100000</v>
       </c>
-      <c r="J4" s="4" t="inlineStr">
+      <c r="K4" s="4" t="inlineStr">
         <is>
           <t>월</t>
         </is>
       </c>
-      <c r="K4" s="9" t="inlineStr">
+      <c r="L4" s="9" t="inlineStr">
         <is>
           <t>기말</t>
         </is>
       </c>
-      <c r="L4" s="7" t="n">
+      <c r="M4" s="7" t="n">
         <v>0.0646424</v>
       </c>
-      <c r="M4" s="16">
-        <f>0</f>
-        <v/>
-      </c>
       <c r="N4" s="16">
         <f>0</f>
         <v/>
@@ -884,14 +886,18 @@
         <f>0</f>
         <v/>
       </c>
-      <c r="Q4" s="16" t="n">
+      <c r="Q4" s="16">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="R4" s="16" t="n">
         <v>110000</v>
       </c>
-      <c r="R4" s="16">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="S4" t="inlineStr">
+      <c r="S4" s="16">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="T4" s="0" t="inlineStr">
         <is>
           <t>판관비</t>
         </is>
@@ -931,26 +937,27 @@
         <f>DATEDIF(E5,F5,"M")+1</f>
         <v/>
       </c>
-      <c r="I5" s="16" t="n">
+      <c r="I5" s="9" t="inlineStr">
+        <is>
+          <t>당월</t>
+        </is>
+      </c>
+      <c r="J5" s="16" t="n">
         <v>1399090</v>
       </c>
-      <c r="J5" s="4" t="inlineStr">
+      <c r="K5" s="4" t="inlineStr">
         <is>
           <t>월</t>
         </is>
       </c>
-      <c r="K5" s="9" t="inlineStr">
+      <c r="L5" s="9" t="inlineStr">
         <is>
           <t>기말</t>
         </is>
       </c>
-      <c r="L5" s="7" t="n">
+      <c r="M5" s="7" t="n">
         <v>0.05499</v>
       </c>
-      <c r="M5" s="16">
-        <f>0</f>
-        <v/>
-      </c>
       <c r="N5" s="16">
         <f>0</f>
         <v/>
@@ -963,14 +970,18 @@
         <f>0</f>
         <v/>
       </c>
-      <c r="Q5" s="16" t="n">
+      <c r="Q5" s="16">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="R5" s="16" t="n">
         <v>17416000</v>
       </c>
-      <c r="R5" s="16">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="S5" t="inlineStr">
+      <c r="S5" s="16">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="T5" s="0" t="inlineStr">
         <is>
           <t>판관비</t>
         </is>
@@ -1010,26 +1021,27 @@
         <f>DATEDIF(E6,F6,"M")</f>
         <v/>
       </c>
-      <c r="I6" s="16" t="n">
+      <c r="I6" s="9" t="inlineStr">
+        <is>
+          <t>당월</t>
+        </is>
+      </c>
+      <c r="J6" s="16" t="n">
         <v>710500</v>
       </c>
-      <c r="J6" s="4" t="inlineStr">
+      <c r="K6" s="4" t="inlineStr">
         <is>
           <t>월</t>
         </is>
       </c>
-      <c r="K6" s="9" t="inlineStr">
+      <c r="L6" s="9" t="inlineStr">
         <is>
           <t>기말</t>
         </is>
       </c>
-      <c r="L6" s="7" t="n">
+      <c r="M6" s="7" t="n">
         <v>0.1094</v>
       </c>
-      <c r="M6" s="16">
-        <f>0</f>
-        <v/>
-      </c>
       <c r="N6" s="16">
         <f>0</f>
         <v/>
@@ -1042,48 +1054,57 @@
         <f>0</f>
         <v/>
       </c>
-      <c r="Q6" s="16" t="n">
+      <c r="Q6" s="16">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="R6" s="16" t="n">
         <v>8670000</v>
       </c>
-      <c r="R6" s="16">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="S6" t="inlineStr">
+      <c r="S6" s="16">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="T6" s="0" t="inlineStr">
         <is>
           <t>판관비</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="I7" s="16" t="n"/>
-      <c r="K7" s="3" t="n"/>
-      <c r="L7" s="7" t="n"/>
-      <c r="N7" s="16" t="n"/>
+      <c r="I7" s="9" t="n"/>
+      <c r="J7" s="16" t="n"/>
+      <c r="L7" s="3" t="n"/>
+      <c r="M7" s="7" t="n"/>
       <c r="O7" s="16" t="n"/>
       <c r="P7" s="16" t="n"/>
       <c r="Q7" s="16" t="n"/>
       <c r="R7" s="16" t="n"/>
+      <c r="S7" s="16" t="n"/>
     </row>
     <row r="8">
-      <c r="I8" s="16" t="n"/>
+      <c r="I8" s="9" t="n"/>
+      <c r="J8" s="16" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="4">
+    <mergeCell ref="E1:I1"/>
     <mergeCell ref="A1:D1"/>
-    <mergeCell ref="I1:M1"/>
-    <mergeCell ref="E1:H1"/>
-    <mergeCell ref="N1:R1"/>
+    <mergeCell ref="J1:N1"/>
+    <mergeCell ref="O1:S1"/>
   </mergeCells>
-  <dataValidations count="3">
+  <dataValidations count="4">
     <dataValidation sqref="G3:G6" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>"O,X"</formula1>
     </dataValidation>
-    <dataValidation sqref="J3:J6" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
+    <dataValidation sqref="K3:K6" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>"월,분기,반기,연"</formula1>
     </dataValidation>
-    <dataValidation sqref="K3:K6" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
+    <dataValidation sqref="L3:L6" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>"기초, 기말"</formula1>
+    </dataValidation>
+    <dataValidation sqref="I3:I8" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
+      <formula1>"당월,익월"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
